--- a/dataset/review result/c_result_gpt-4-turbo-preview_2024-04-06 18_24_54.xlsx
+++ b/dataset/review result/c_result_gpt-4-turbo-preview_2024-04-06 18_24_54.xlsx
@@ -5,17 +5,21 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oywy2\Desktop\dataset\review result\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\LLM-CMT\dataset\review result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28F4BC86-91E0-4C23-BA0D-1E3DE3E85AD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F073E44-7131-4894-B72F-12590F3817E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="-36345" yWindow="6945" windowWidth="19200" windowHeight="9765" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="-31125" yWindow="5100" windowWidth="29190" windowHeight="12525" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="c_result_gpt-4-turbo-preview_20" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="c_result_gpt-4-turbo-preview_20" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="10" r:id="rId3"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="150">
   <si>
     <t>absolute_path</t>
   </si>
@@ -473,6 +477,15 @@
   <si>
     <t>Use of MD5 for hashing</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行标签</t>
+  </si>
+  <si>
+    <t>(空白)</t>
+  </si>
+  <si>
+    <t>总计</t>
   </si>
 </sst>
 </file>
@@ -519,10 +532,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -751,6 +768,367 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="欧阳文宜" refreshedDate="45445.676079398145" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="58" xr:uid="{6FD593D6-4632-4BCA-809B-988DFD9A1D6B}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="B1:B1048576" sheet="c_result_gpt-4-turbo-preview_20"/>
+  </cacheSource>
+  <cacheFields count="1">
+    <cacheField name="filename" numFmtId="0">
+      <sharedItems containsBlank="1" count="26">
+        <s v="57048cryptohash_openssl.c"/>
+        <s v="57048be-secure-openssl.c"/>
+        <s v="57048fe-secure-openssl.c"/>
+        <s v="57048pg_strong_random.c"/>
+        <s v="816lcfs-fsverity.c"/>
+        <s v="438transform_aes.c"/>
+        <s v="438transform_cc20.c"/>
+        <s v="510fuzz_crypto.c"/>
+        <s v="510x509_afl.c"/>
+        <s v="510x509_sydr.c"/>
+        <s v="57048pgp-mpi-openssl.c"/>
+        <s v="57048hmac_openssl.c"/>
+        <s v="57048openssl.c"/>
+        <s v="510fuzz_verify_cert.c"/>
+        <s v="510crl_afl.c"/>
+        <s v="510crl_sydr.c"/>
+        <s v="510cms_afl.c"/>
+        <s v="510cms_sydr.c"/>
+        <s v="510client_sydr.c"/>
+        <s v="510cmp_afl.c"/>
+        <s v="510cmp_sydr.c"/>
+        <s v="510client_afl.c"/>
+        <s v="510bignum_afl.c"/>
+        <s v="510bignum_sydr.c"/>
+        <s v="510asn1_afl.c"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="58">
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="16"/>
+  </r>
+  <r>
+    <x v="17"/>
+  </r>
+  <r>
+    <x v="18"/>
+  </r>
+  <r>
+    <x v="18"/>
+  </r>
+  <r>
+    <x v="18"/>
+  </r>
+  <r>
+    <x v="19"/>
+  </r>
+  <r>
+    <x v="20"/>
+  </r>
+  <r>
+    <x v="21"/>
+  </r>
+  <r>
+    <x v="21"/>
+  </r>
+  <r>
+    <x v="22"/>
+  </r>
+  <r>
+    <x v="23"/>
+  </r>
+  <r>
+    <x v="24"/>
+  </r>
+  <r>
+    <x v="24"/>
+  </r>
+  <r>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="25"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CFDB179D-6C86-4DDE-9C30-3023F9C2975C}" name="数据透视表2" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:A30" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="1">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="27">
+        <item x="5"/>
+        <item x="6"/>
+        <item x="24"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="21"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="7"/>
+        <item x="13"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="3"/>
+        <item x="10"/>
+        <item x="4"/>
+        <item x="25"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="27">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="24"/>
+    </i>
+    <i>
+      <x v="25"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pivotTableStyleInfo name="PivotStylePreset2_Accent1" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1010,6 +1388,160 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB320CE5-927E-4542-8C19-8E165CD32881}">
+  <dimension ref="A3:A30"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="26.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A14" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A15" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A16" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A22" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A24" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A25" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A26" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A27" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A28" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A29" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A30" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
